--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -2985,34 +2985,34 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>5355000</v>
+        <v>4658800</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>26510</v>
+        <v>23063</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>4658850</v>
+        <v>4658800</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>23064</v>
+        <v>23063</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -11422,14 +11422,14 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
         <v>4505700</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>22305</v>
+        <v>22416</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>4505700</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>22305</v>
+        <v>22416</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
@@ -12161,34 +12161,34 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>5498000</v>
+        <v>4783200</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>25220</v>
+        <v>21941</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>4783260</v>
+        <v>4783200</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>21942</v>
+        <v>21941</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -13029,34 +13029,34 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
-        <v>8313000</v>
+        <v>7232300</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>24522</v>
+        <v>21334</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K200" s="5" t="n">
-        <v>7232310</v>
+        <v>7232300</v>
       </c>
       <c r="L200" s="5" t="n">
         <v>21334</v>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N200" s="3" t="inlineStr">
@@ -14083,23 +14083,23 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
-        <v>5060000</v>
+        <v>4402200</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>25050</v>
+        <v>21793</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K217" s="5" t="n">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N217" s="3" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21372,12 +21372,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
-$536万
-$26,510/呎
-(在售)</t>
+$466万
+$23,063/呎
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -22509,10 +22509,10 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>C | 202呎 (开放式)
+          <t>C | 201呎 (开放式)
 $451万
-$22,305/呎
-(26年-07月-17日)</t>
+$22,416/呎
+(26年-08月-04日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -22658,12 +22658,12 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
-$550万
-$25,220/呎
-(在售)</t>
+$478万
+$21,941/呎
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -22793,12 +22793,12 @@
 (26年-06月-22日)</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 339呎 (1房)
-$831万
-$24,522/呎
-(在售)</t>
+$723万
+$21,334/呎
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -22904,12 +22904,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
-$506万
-$25,050/呎
-(在售)</t>
+$440万
+$21,793/呎
+(26年-08月-08日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -23028,7 +23028,7 @@
           <t>D | 202呎 (开放式)
 $440万
 $21,771/呎
-(26年-07月-09日)</t>
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -23536,7 +23536,7 @@
           <t>D | 202呎 (开放式)
 $434万
 $21,500/呎
-(26年-07月-28日)</t>
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -15881,34 +15881,34 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
-        <v>5329000</v>
+        <v>4636200</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>24445</v>
+        <v>21267</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K246" s="5" t="n">
-        <v>4636230</v>
+        <v>4636200</v>
       </c>
       <c r="L246" s="5" t="n">
         <v>21267</v>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23166,12 +23166,12 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
-$533万
-$24,445/呎
-(在售)</t>
+$464万
+$21,267/呎
+(26年-08月-11日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -7511,34 +7511,34 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
-        <v>5582000</v>
+        <v>4856300</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>25606</v>
+        <v>22277</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="5" t="n">
-        <v>4856340</v>
+        <v>4856300</v>
       </c>
       <c r="L111" s="5" t="n">
         <v>22277</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -22023,12 +22023,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
-$558万
-$25,606/呎
-(在售)</t>
+$486万
+$22,277/呎
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -23179,7 +23179,7 @@
           <t>G | 339呎 (1房)
 $710万
 $20,944/呎
-(26年-07月-28日)</t>
+(26年-08月-13日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12166,14 +12166,14 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
         <v>4783200</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>21941</v>
+        <v>22042</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>4783200</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>21941</v>
+        <v>22042</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -21377,7 +21377,7 @@
           <t>D | 202呎 (开放式)
 $466万
 $23,063/呎
-(26年-08月-06日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -22660,10 +22660,10 @@
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>F | 218呎 (开放式)
+          <t>F | 217呎 (开放式)
 $478万
-$21,941/呎
-(26年-08月-07日)</t>
+$22,042/呎
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -22909,7 +22909,7 @@
           <t>E | 202呎 (开放式)
 $440万
 $21,793/呎
-(26年-08月-08日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -4721,34 +4721,34 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>5633000</v>
+        <v>4900700</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>25839</v>
+        <v>22480</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="5" t="n">
-        <v>4900710</v>
+        <v>4900700</v>
       </c>
       <c r="L66" s="5" t="n">
         <v>22480</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -6643,34 +6643,34 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>5247000</v>
+        <v>4564800</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>25975</v>
+        <v>22598</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="5" t="n">
-        <v>4564890</v>
+        <v>4564800</v>
       </c>
       <c r="L97" s="5" t="n">
         <v>22598</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
@@ -14145,34 +14145,34 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
-        <v>5102000</v>
+        <v>4438700</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>25257</v>
+        <v>21974</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K218" s="5" t="n">
-        <v>4438740</v>
+        <v>4438700</v>
       </c>
       <c r="L218" s="5" t="n">
         <v>21974</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21642,12 +21642,12 @@
 (26年-02月-13日)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 218呎 (开放式)
-$563万
-$25,839/呎
-(在售)</t>
+$490万
+$22,480/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -21888,12 +21888,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 202呎 (开放式)
-$525万
-$25,975/呎
-(在售)</t>
+$456万
+$22,598/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -22896,12 +22896,12 @@
 (26年-06月-16日)</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 202呎 (开放式)
-$510万
-$25,257/呎
-(在售)</t>
+$444万
+$21,974/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -20657,34 +20657,34 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
-        <v>5007000</v>
+        <v>4356000</v>
       </c>
       <c r="I322" s="5" t="n">
-        <v>27817</v>
+        <v>24200</v>
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K322" s="5" t="n">
-        <v>4356090</v>
+        <v>4356000</v>
       </c>
       <c r="L322" s="5" t="n">
         <v>24200</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 100天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N322" s="3" t="inlineStr">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23793,12 +23793,12 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 180呎 (开放式)
-$501万
-$27,817/呎
-(在售)</t>
+$436万
+$24,200/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．曦汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．曦汇.xlsx
@@ -11360,7 +11360,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -22520,7 +22520,7 @@
           <t>D | 202呎 (开放式)
 $454万
 $22,452/呎
-(26年-07月-05日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
